--- a/Samples/patient_moderate_risk_full.xlsx
+++ b/Samples/patient_moderate_risk_full.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,412 +429,412 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>admission_type_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>discharge_disposition_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>admission_source_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>time_in_hospital</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>num_lab_procedures</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>num_procedures</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>num_medications</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>number_outpatient</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>number_emergency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>number_inpatient</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>number_diagnoses</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>diabetes_diag_count</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>comorbidity_count</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>metformin_encoded</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>metformin_active</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>repaglinide_encoded</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>repaglinide_active</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>nateglinide_encoded</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>nateglinide_active</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>chlorpropamide_encoded</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>chlorpropamide_active</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>glimepiride_encoded</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>glimepiride_active</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>acetohexamide_encoded</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>acetohexamide_active</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>glipizide_encoded</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>glipizide_active</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>glyburide_encoded</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>glyburide_active</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>tolbutamide_encoded</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>tolbutamide_active</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pioglitazone_encoded</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>pioglitazone_active</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>rosiglitazone_encoded</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>rosiglitazone_active</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>acarbose_encoded</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>acarbose_active</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>miglitol_encoded</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>miglitol_active</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>troglitazone_encoded</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>troglitazone_active</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>tolazamide_encoded</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>tolazamide_active</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>examide_encoded</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>examide_active</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>citoglipton_encoded</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>citoglipton_active</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>insulin_encoded</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>insulin_active</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>glyburide-metformin_encoded</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>glyburide-metformin_active</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>glipizide-metformin_encoded</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>glipizide-metformin_active</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>glimepiride-pioglitazone_encoded</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>glimepiride-pioglitazone_active</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>metformin-rosiglitazone_encoded</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>metformin-rosiglitazone_active</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>metformin-pioglitazone_encoded</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>metformin-pioglitazone_active</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>total_medications</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>on_insulin</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>oral_medications</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>change_encoded</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>diabetesMed_encoded</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>age_numeric</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>is_elderly</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>total_prior_admissions</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>emergency_ratio</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>inpatient_ratio</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>long_stay</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>total_procedures</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>high_lab_utilization</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>high_diagnosis_count</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>emergency_admission</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>not_home_discharge</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>er_admission</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>age_comorbidity_interaction</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>med_per_comorbidity</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>admissions_per_year</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>emerg_inpatient_combo</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>insulin_complexity</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>diabetes_med_intensity</t>
         </is>
@@ -839,34 +851,34 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -1007,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -1022,13 +1034,13 @@
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BP2" t="n">
         <v>0.33</v>
@@ -1040,34 +1052,34 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>240</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CA2" t="n">
         <v>2</v>
       </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>165</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1</v>
-      </c>
       <c r="CB2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
